--- a/output/pdf_financials_xlsx/MONT.xlsx
+++ b/output/pdf_financials_xlsx/MONT.xlsx
@@ -6058,43 +6058,43 @@
         <v>0.170248</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.199833</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.224859</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.25496</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.295188</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.654436</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.923538</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.214258</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.383282</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0.08207</v>
+        <v>1.547129</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0.06837</v>
+        <v>1.676684</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0.044144</v>
+        <v>2.147714</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0.08207</v>
+        <v>2.999091</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0.08207</v>
+        <v>3.172755</v>
       </c>
     </row>
     <row r="93">
@@ -11232,7 +11232,11 @@
           <t>Share-based payments reserve (Note 12)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -21992,7 +21996,11 @@
           <t>Share-based payments reserve (Note 15)</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -25952,7 +25960,11 @@
           <t>Share-based payments reserve (Note 14)</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -28860,7 +28872,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -35954,7 +35970,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
           <t>-</t>
@@ -37039,7 +37059,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MONT.xlsx
+++ b/output/pdf_financials_xlsx/MONT.xlsx
@@ -1089,19 +1089,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.007783</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.004087</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.00881</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.013542</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.009856</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1110,13 +1110,13 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.070595</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.594491</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.960545</v>
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
@@ -2131,19 +2131,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.080577</v>
+        <v>-0.08835999999999999</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.192084</v>
+        <v>-0.196171</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.651347</v>
+        <v>0.642537</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.209129</v>
+        <v>-0.222671</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.014949</v>
+        <v>-1.024805</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.994858</v>
@@ -2152,13 +2152,13 @@
         <v>-0.156633</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.39169</v>
+        <v>0.321095</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.424951</v>
+        <v>-1.019442</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.19762</v>
+        <v>-1.158165</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -2259,19 +2259,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.080577</v>
+        <v>-0.08835999999999999</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.192084</v>
+        <v>-0.196171</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.651347</v>
+        <v>0.642537</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.209129</v>
+        <v>-0.222671</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.014949</v>
+        <v>-1.024805</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.994858</v>
@@ -2280,13 +2280,13 @@
         <v>-0.156633</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.39169</v>
+        <v>0.321095</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.424951</v>
+        <v>-1.019442</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.19762</v>
+        <v>-1.158165</v>
       </c>
       <c r="L29" s="1" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-1038.268510751478</v>
+        <v>-1048.350962620455</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>-4706.9360333081</v>
@@ -2352,13 +2352,13 @@
         <v>-251.6031098403316</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>287.1669672575844</v>
+        <v>235.4103432601651</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-69.15495914504849</v>
+        <v>-165.9002328756646</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-18.98558452101317</v>
+        <v>-111.2662660498898</v>
       </c>
       <c r="L30" s="1" t="inlineStr">
         <is>
@@ -2569,19 +2569,19 @@
         <v>0.121259</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.05798</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.01465</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.409871</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.217355</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.713792</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>3.749949</v>
@@ -2590,19 +2590,19 @@
         <v>4.662156</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>12.872769</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>9.314526000000001</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>7.008311</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>6.846487</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>2.028712</v>
       </c>
     </row>
     <row r="35">
@@ -2685,19 +2685,19 @@
         <v>0.121259</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.05798</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.01465</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.409871</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.217355</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.713792</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>3.749949</v>
@@ -2706,19 +2706,19 @@
         <v>4.662156</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>12.872769</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>9.314526000000001</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>7.008311</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>6.846487</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>2.028712</v>
       </c>
     </row>
     <row r="37">
@@ -7901,13 +7901,13 @@
         <v>0</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.094735</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.07815900000000001</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.343181</v>
       </c>
     </row>
     <row r="125">
@@ -7959,13 +7959,13 @@
         <v>0</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.094735</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.07815900000000001</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.343181</v>
       </c>
     </row>
     <row r="126">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -14892,7 +14892,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -20131,7 +20131,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -41972,7 +41972,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -65442,7 +65446,7 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
@@ -66107,7 +66111,7 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
@@ -67857,7 +67861,7 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
@@ -69453,7 +69457,7 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
@@ -70447,7 +70451,7 @@
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
@@ -72675,7 +72679,7 @@
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E648" s="5" t="n">

--- a/output/pdf_financials_xlsx/MONT.xlsx
+++ b/output/pdf_financials_xlsx/MONT.xlsx
@@ -768,31 +768,31 @@
         <v>0.005346</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.031145</v>
+        <v>0.034145</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.016133</v>
+        <v>0.055605</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.015655</v>
+        <v>0.113462</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.014762</v>
+        <v>0.055293</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.017382</v>
+        <v>0.064303</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.013109</v>
+        <v>0.054599</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.022015</v>
+        <v>0.106998</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.02721</v>
+        <v>0.238133</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.028379</v>
+        <v>0.328081</v>
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
@@ -1896,10 +1896,8 @@
       <c r="Q23" s="3" t="n">
         <v>-12.502724</v>
       </c>
-      <c r="R23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R23" s="3" t="n">
+        <v>-5.78532</v>
       </c>
     </row>
     <row r="24">
@@ -2941,7 +2939,7 @@
         <v>0</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>0.114052</v>
       </c>
       <c r="P40" s="3" t="n">
         <v>2.088735</v>
@@ -2999,7 +2997,7 @@
         <v>26.765996</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>36.323492</v>
+        <v>36.437544</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>2.933182</v>
@@ -6448,12 +6446,10 @@
         <v>3.93169</v>
       </c>
       <c r="Q99" s="3" t="n">
-        <v>-12.502724</v>
-      </c>
-      <c r="R99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-10.918864</v>
+      </c>
+      <c r="R99" s="3" t="n">
+        <v>-5.78532</v>
       </c>
     </row>
     <row r="100">
@@ -7278,7 +7274,7 @@
         <v>0</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0</v>
+        <v>1.43145</v>
       </c>
       <c r="D114" s="3" t="n">
         <v>-0.026375</v>
@@ -7360,10 +7356,10 @@
         <v>0</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M115" s="3" t="n">
         <v>0</v>
@@ -39378,7 +39374,11 @@
           <t>Net loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -39576,7 +39576,11 @@
           <t>Deferred tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
           <t>-</t>
@@ -42964,7 +42968,11 @@
           <t>Current and deferred tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E349" t="inlineStr">
         <is>
           <t>-</t>
@@ -47207,7 +47215,11 @@
           <t>Deferred tax expenses</t>
         </is>
       </c>
-      <c r="D392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E392" t="inlineStr">
         <is>
           <t>-</t>
@@ -51945,7 +51957,11 @@
           <t>Proceeds from sale of co-investments</t>
         </is>
       </c>
-      <c r="D440" t="inlineStr"/>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E440" t="inlineStr">
         <is>
           <t>-</t>
@@ -59509,7 +59525,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D516" t="inlineStr"/>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E516" t="inlineStr">
         <is>
           <t>-</t>
@@ -61717,7 +61737,11 @@
           <t>Future income tax expense</t>
         </is>
       </c>
-      <c r="D538" t="inlineStr"/>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E538" t="inlineStr">
         <is>
           <t>-</t>
@@ -63244,7 +63268,11 @@
           <t>Shares issued for acquisition of investments</t>
         </is>
       </c>
-      <c r="D553" t="inlineStr"/>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E553" t="inlineStr">
         <is>
           <t>-</t>
@@ -65745,7 +65773,11 @@
           <t>Administrative, management, and directors fees (Note 9)</t>
         </is>
       </c>
-      <c r="D578" t="inlineStr"/>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E578" t="inlineStr">
         <is>
           <t>-</t>
@@ -68067,7 +68099,11 @@
           <t>Administrative, management and directors fees (Note 8)</t>
         </is>
       </c>
-      <c r="D602" t="inlineStr"/>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E602" t="inlineStr">
         <is>
           <t>-</t>
@@ -69063,7 +69099,11 @@
           <t>Administrative, management and directors fees (Note 6)</t>
         </is>
       </c>
-      <c r="D612" t="inlineStr"/>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E612" t="inlineStr">
         <is>
           <t>-</t>
@@ -69358,7 +69398,11 @@
           <t>Administrative, management, and directors fees (Note 5)</t>
         </is>
       </c>
-      <c r="D615" t="inlineStr"/>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E615" t="inlineStr">
         <is>
           <t>-</t>
@@ -69857,7 +69901,11 @@
           <t>DEFERRED INCOME TAX RECOVERY</t>
         </is>
       </c>
-      <c r="D620" t="inlineStr"/>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E620" t="inlineStr">
         <is>
           <t>-</t>
@@ -69958,7 +70006,11 @@
           <t>Administrative, management, and directors fees (Note 7) $</t>
         </is>
       </c>
-      <c r="D621" t="inlineStr"/>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E621" t="inlineStr">
         <is>
           <t>-</t>
@@ -70653,7 +70705,11 @@
           <t>FUTURE INCOME TAX RECOVERY (EXPENSE)</t>
         </is>
       </c>
-      <c r="D628" t="inlineStr"/>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E628" t="inlineStr">
         <is>
           <t>-</t>
@@ -71146,7 +71202,11 @@
           <t>Administrative, management, and directors fees (Note 8) $</t>
         </is>
       </c>
-      <c r="D633" t="inlineStr"/>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E633" t="inlineStr">
         <is>
           <t>-</t>
